--- a/direct/model_outputs/aov2_formatted.xlsx
+++ b/direct/model_outputs/aov2_formatted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rtbat\Dropbox\Agri_Contaminants\direct\model_outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{61EFD353-E1B8-44DE-B8F7-DE40B059DB1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6F1FACD-06B8-43B6-BF20-088EE6F12A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8D7FD050-FC9A-45F7-9E49-6378F62C4CB8}"/>
   </bookViews>
@@ -958,12 +958,8 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -973,89 +969,80 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="10" xfId="39" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" xfId="39" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="11" xfId="39" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="11" xfId="39" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="10" xfId="39" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" xfId="39" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="11" xfId="39" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="11" xfId="39" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1432,14 +1419,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{838449DB-9D96-4916-AB36-4502BABED3C6}">
-  <dimension ref="B1:J17"/>
+  <dimension ref="B1:J16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="39.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="39.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25.44140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="24.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="23.33203125" bestFit="1" customWidth="1"/>
@@ -1447,445 +1434,439 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6" t="s">
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
     </row>
     <row r="2" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="5" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="28"/>
-      <c r="G3" s="10" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="9" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="15" t="s">
+      <c r="J4" s="12" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="F5" s="28"/>
-      <c r="G5" s="10" t="s">
+      <c r="F5" s="14"/>
+      <c r="G5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="17" t="s">
+      <c r="J5" s="14" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="30" t="s">
+      <c r="F6" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="20" t="s">
+      <c r="H6" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="20" t="s">
+      <c r="I6" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="J6" s="21" t="s">
+      <c r="J6" s="18" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="31" t="s">
+      <c r="F7" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I7" s="22" t="s">
+      <c r="I7" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="17" t="s">
+      <c r="J7" s="14" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="E8" s="23" t="s">
+      <c r="E8" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="F8" s="30" t="s">
+      <c r="F8" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="H8" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="I8" s="19" t="s">
+      <c r="I8" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="J8" s="21" t="s">
+      <c r="J8" s="18" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="F9" s="28"/>
-      <c r="G9" s="10" t="s">
+      <c r="F9" s="14"/>
+      <c r="G9" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J9" s="17" t="s">
+      <c r="J9" s="14" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="32"/>
-      <c r="G10" s="19" t="s">
+      <c r="F10" s="18"/>
+      <c r="G10" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="20" t="s">
+      <c r="H10" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="20" t="s">
+      <c r="I10" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="J10" s="21" t="s">
+      <c r="J10" s="18" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="11" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="F11" s="31" t="s">
+      <c r="F11" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="G11" s="22" t="s">
+      <c r="G11" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="I11" s="11" t="s">
+      <c r="I11" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="J11" s="17" t="s">
+      <c r="J11" s="14" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="12" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E12" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="F12" s="30" t="s">
+      <c r="F12" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="H12" s="19" t="s">
+      <c r="H12" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="20" t="s">
+      <c r="I12" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="21" t="s">
+      <c r="J12" s="18" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="F13" s="28"/>
-      <c r="G13" s="11" t="s">
+      <c r="F13" s="14"/>
+      <c r="G13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="H13" s="11" t="s">
+      <c r="H13" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="J13" s="17" t="s">
+      <c r="J13" s="14" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="F14" s="32"/>
-      <c r="G14" s="20" t="s">
+      <c r="F14" s="18"/>
+      <c r="G14" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="H14" s="20" t="s">
+      <c r="H14" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="I14" s="20" t="s">
+      <c r="I14" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="J14" s="21" t="s">
+      <c r="J14" s="18" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="15" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="31" t="s">
+      <c r="F15" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="G15" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="H15" s="10" t="s">
+      <c r="H15" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="J15" s="17" t="s">
+      <c r="J15" s="14" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="26" t="s">
+      <c r="D16" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="E16" s="26" t="s">
+      <c r="E16" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="F16" s="33"/>
-      <c r="G16" s="26" t="s">
+      <c r="F16" s="24"/>
+      <c r="G16" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="H16" s="26" t="s">
+      <c r="H16" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="I16" s="26" t="s">
+      <c r="I16" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="J16" s="27" t="s">
+      <c r="J16" s="24" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="2"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:F31">
